--- a/excel_templates/invoice.xlsx
+++ b/excel_templates/invoice.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15105" windowHeight="8070"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="开票审批" sheetId="19" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>{{title}}增值税发票开票审批单</t>
   </si>
@@ -117,13 +117,13 @@
     </r>
   </si>
   <si>
-    <t>{{Proxy client}}</t>
+    <t>{{Proxy_client}}</t>
   </si>
   <si>
     <t>纳税人登记号</t>
   </si>
   <si>
-    <t>{{Registration Number}}</t>
+    <t>{{Registration_Number}}</t>
   </si>
   <si>
     <t>地址电话</t>
@@ -135,13 +135,10 @@
     <t>开户银行及帐号</t>
   </si>
   <si>
-    <t>{{bank of deposit}}</t>
+    <t>{{bank_of_deposit}}</t>
   </si>
   <si>
     <t>{{account}}</t>
-  </si>
-  <si>
-    <t>海田控股</t>
   </si>
   <si>
     <r>
@@ -333,9 +330,6 @@
     <t>代理费</t>
   </si>
   <si>
-    <t>大洲进出口</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -410,7 +404,7 @@
     </r>
   </si>
   <si>
-    <t>{{Contract No.}}</t>
+    <t>{{Contract_No.}}</t>
   </si>
   <si>
     <t>销货
@@ -674,14 +668,14 @@
       <b/>
       <sz val="10.5"/>
       <color indexed="8"/>
-      <name val="Times New Roman"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1690,7 +1684,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -1702,7 +1696,7 @@
     <col min="11" max="11" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -1717,7 +1711,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="1"/>
@@ -1732,7 +1726,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="1"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
@@ -1747,7 +1741,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" ht="33" customHeight="1" spans="1:14">
+    <row r="4" ht="33" customHeight="1" spans="1:13">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>0</v>
@@ -1764,7 +1758,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:13">
       <c r="A5" s="1"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
@@ -1779,7 +1773,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:14">
+    <row r="6" ht="22.5" customHeight="1" spans="1:13">
       <c r="A6" s="1"/>
       <c r="B6" s="10" t="s">
         <v>1</v>
@@ -1804,7 +1798,7 @@
       <c r="L6" s="9"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" customHeight="1" spans="1:14">
+    <row r="7" customHeight="1" spans="1:13">
       <c r="A7" s="1"/>
       <c r="B7" s="14"/>
       <c r="C7" s="11" t="s">
@@ -1827,7 +1821,7 @@
       <c r="L7" s="9"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" ht="25.5" customHeight="1" spans="1:14">
+    <row r="8" ht="25.5" customHeight="1" spans="1:13">
       <c r="A8" s="1"/>
       <c r="B8" s="16"/>
       <c r="C8" s="11"/>
@@ -1843,43 +1837,40 @@
       <c r="K8" s="18"/>
       <c r="L8" s="9"/>
       <c r="M8" s="1"/>
-      <c r="N8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:14">
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
       <c r="A9" s="1"/>
       <c r="B9" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="I9" s="12" t="s">
         <v>16</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>17</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L9" s="9"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" ht="31.5" customHeight="1" spans="1:14">
+    <row r="10" ht="31.5" customHeight="1" spans="1:13">
       <c r="A10" s="1"/>
       <c r="B10" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="19"/>
@@ -1892,11 +1883,8 @@
       <c r="K10" s="22"/>
       <c r="L10" s="9"/>
       <c r="M10" s="1"/>
-      <c r="N10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" ht="23.25" customHeight="1" spans="1:14">
+    </row>
+    <row r="11" ht="23.25" customHeight="1" spans="1:13">
       <c r="A11" s="1"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -1911,7 +1899,7 @@
       <c r="L11" s="9"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" ht="23.25" customHeight="1" spans="1:14">
+    <row r="12" ht="23.25" customHeight="1" spans="1:13">
       <c r="A12" s="1"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -1926,7 +1914,7 @@
       <c r="L12" s="9"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" ht="23.25" customHeight="1" spans="1:14">
+    <row r="13" ht="23.25" customHeight="1" spans="1:13">
       <c r="A13" s="1"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -1941,10 +1929,10 @@
       <c r="L13" s="9"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" ht="23.25" customHeight="1" spans="1:14">
+    <row r="14" ht="23.25" customHeight="1" spans="1:13">
       <c r="A14" s="1"/>
       <c r="B14" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" s="23">
         <f>I10</f>
@@ -1955,26 +1943,26 @@
       <c r="F14" s="23"/>
       <c r="G14" s="23"/>
       <c r="H14" s="20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="9"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" ht="23.25" customHeight="1" spans="1:14">
+    <row r="15" ht="23.25" customHeight="1" spans="1:13">
       <c r="A15" s="1"/>
       <c r="B15" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>24</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>26</v>
       </c>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
@@ -1984,13 +1972,13 @@
       </c>
       <c r="I15" s="25"/>
       <c r="J15" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K15" s="27"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" ht="34.5" customHeight="1" spans="1:14">
+    <row r="16" ht="34.5" customHeight="1" spans="1:13">
       <c r="A16" s="1"/>
       <c r="B16" s="28"/>
       <c r="C16" s="29" t="s">
@@ -2003,11 +1991,11 @@
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
       <c r="H16" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I16" s="25"/>
       <c r="J16" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K16" s="27"/>
       <c r="L16" s="1"/>

--- a/excel_templates/invoice.xlsx
+++ b/excel_templates/invoice.xlsx
@@ -404,7 +404,7 @@
     </r>
   </si>
   <si>
-    <t>{{Contract_No.}}</t>
+    <t>{{Contract_No}}</t>
   </si>
   <si>
     <t>销货
@@ -668,14 +668,14 @@
       <b/>
       <sz val="10.5"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <color indexed="8"/>
-      <name val="Times New Roman"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>

--- a/excel_templates/invoice.xlsx
+++ b/excel_templates/invoice.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>{{title}}增值税发票开票审批单</t>
   </si>
@@ -129,7 +129,7 @@
     <t>地址电话</t>
   </si>
   <si>
-    <t>{{address}}</t>
+    <t>{{kh_address}}</t>
   </si>
   <si>
     <t>开户银行及帐号</t>
@@ -418,6 +418,9 @@
   </si>
   <si>
     <t>{{tax}}</t>
+  </si>
+  <si>
+    <t>{{address}}</t>
   </si>
   <si>
     <t>开户银行及账号</t>
@@ -1985,17 +1988,17 @@
         <v>6</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
       <c r="H16" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I16" s="25"/>
       <c r="J16" s="26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" s="27"/>
       <c r="L16" s="1"/>
